--- a/Bibsam_tidskriftslistor/scifree_data_johnbenjamin.xlsx
+++ b/Bibsam_tidskriftslistor/scifree_data_johnbenjamin.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28227"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="8" documentId="11_FA850B1B9BF82AB29021F79D0B027AC9DA6FA7F0" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A370FA3B-E967-4C6F-ABFB-4CFF2B7EAB47}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A2B52945-FC7C-4F22-AAFD-8E03C949CE31}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="2" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="3" r:id="rId1"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="623" uniqueCount="363">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="616" uniqueCount="359">
   <si>
     <t>Open</t>
   </si>
@@ -151,9 +151,6 @@
     <t>Journal of Asian Pacific Communication</t>
   </si>
   <si>
-    <t>Journal of English for Research Publication Purposes</t>
-  </si>
-  <si>
     <t>Journal of English-Medium Instruction</t>
   </si>
   <si>
@@ -259,9 +256,6 @@
     <t>Review of Cognitive Linguistics</t>
   </si>
   <si>
-    <t>Revista Española de Lingüística Aplicada/Spanish Journal of Applied Linguistics</t>
-  </si>
-  <si>
     <t>Revue Romane</t>
   </si>
   <si>
@@ -406,9 +400,6 @@
     <t>1569-9838</t>
   </si>
   <si>
-    <t>2590-1001</t>
-  </si>
-  <si>
     <t>2666-8890</t>
   </si>
   <si>
@@ -514,9 +505,6 @@
     <t>1877-976X</t>
   </si>
   <si>
-    <t>2254-6774</t>
-  </si>
-  <si>
     <t>1600-0811</t>
   </si>
   <si>
@@ -661,9 +649,6 @@
     <t>0957-6851</t>
   </si>
   <si>
-    <t>2590-0994</t>
-  </si>
-  <si>
     <t>2666-8882</t>
   </si>
   <si>
@@ -769,9 +754,6 @@
     <t>1877-9751</t>
   </si>
   <si>
-    <t>0213-2028</t>
-  </si>
-  <si>
     <t>0035-3906</t>
   </si>
   <si>
@@ -919,9 +901,6 @@
     <t>https://benjamins.com/catalog/japc</t>
   </si>
   <si>
-    <t>https://benjamins.com/catalog/jerpp</t>
-  </si>
-  <si>
     <t>https://benjamins.com/catalog/jemi</t>
   </si>
   <si>
@@ -1027,9 +1006,6 @@
     <t>https://benjamins.com/catalog/rcl</t>
   </si>
   <si>
-    <t>https://benjamins.com/catalog/resla</t>
-  </si>
-  <si>
     <t>https://benjamins.com/catalog/rro</t>
   </si>
   <si>
@@ -1109,6 +1085,18 @@
   </si>
   <si>
     <t>http://www.jbe-platform.com/content/journals/29505798</t>
+  </si>
+  <si>
+    <t>2799‑8592</t>
+  </si>
+  <si>
+    <t>2799-6190</t>
+  </si>
+  <si>
+    <t>InContext</t>
+  </si>
+  <si>
+    <t>https://benjamins.com/catalog/ic</t>
   </si>
 </sst>
 </file>
@@ -1164,19 +1152,19 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{382A8B49-C3A4-4BBF-BD4A-0B59EA5AC757}" name="Table2" displayName="Table2" ref="A1:G89" totalsRowShown="0">
-  <autoFilter ref="A1:G89" xr:uid="{382A8B49-C3A4-4BBF-BD4A-0B59EA5AC757}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:G89">
-    <sortCondition ref="D1:D89"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{993614B3-B83E-4DB4-9273-2C36EE727381}" name="Table1" displayName="Table1" ref="A1:G88" totalsRowShown="0">
+  <autoFilter ref="A1:G88" xr:uid="{993614B3-B83E-4DB4-9273-2C36EE727381}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:G88">
+    <sortCondition ref="D1:D88"/>
   </sortState>
   <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{2FD4C316-6DD8-4B81-9212-1984760A02AA}" name="Imprint"/>
-    <tableColumn id="2" xr3:uid="{673491EE-1C5A-4FB2-AA99-4C91B3FE2CEE}" name="ISSN Electronic"/>
-    <tableColumn id="3" xr3:uid="{4F00FB33-F987-4F5D-9EFF-EB277E9DCEE6}" name="ISSN Print"/>
-    <tableColumn id="4" xr3:uid="{DE3EA32F-EC76-4387-98C6-5B489B6FB6E4}" name="Journal Name"/>
-    <tableColumn id="5" xr3:uid="{5DC0BD65-F626-41F1-AF89-B1BE1EDD0586}" name="JournalURL"/>
-    <tableColumn id="6" xr3:uid="{F6E2BFC8-8AD9-4C82-B836-27889290299A}" name="Publishing model"/>
-    <tableColumn id="7" xr3:uid="{D92AE4AB-6761-4E3D-A3F2-5B1EDF73E973}" name="CC License options"/>
+    <tableColumn id="1" xr3:uid="{657FBA63-28AF-43FB-97D0-66E3E2A4E0B5}" name="Imprint"/>
+    <tableColumn id="2" xr3:uid="{A8E520AA-1B32-4C51-94F6-EC84DE7E12BE}" name="ISSN Electronic"/>
+    <tableColumn id="3" xr3:uid="{AAB904CF-CC99-4E2E-BD7F-59AA97408C57}" name="ISSN Print"/>
+    <tableColumn id="4" xr3:uid="{BE444C86-60F1-46DC-994A-F1F3830A58AE}" name="Journal Name"/>
+    <tableColumn id="5" xr3:uid="{244CC34F-ACFA-47F8-B91C-7B7D3D790F90}" name="JournalURL"/>
+    <tableColumn id="6" xr3:uid="{85E1AB3F-176E-40F9-ACD0-04D274058F93}" name="Publishing model"/>
+    <tableColumn id="7" xr3:uid="{25821D45-D43C-4B59-B7F4-C7718C5CAF01}" name="CC License options"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1444,8 +1432,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A45E61CA-3546-40E9-85B2-532C1E35B1D4}">
-  <dimension ref="A1:G89"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{28FA8B0A-ACC5-4E25-8447-CC99D643F617}">
+  <dimension ref="A1:G88"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.7109375" customWidth="1"/>
@@ -1482,19 +1470,19 @@
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>265</v>
+        <v>259</v>
       </c>
       <c r="B2" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="C2" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="D2" t="s">
         <v>10</v>
       </c>
       <c r="E2" t="s">
-        <v>266</v>
+        <v>260</v>
       </c>
       <c r="F2" t="s">
         <v>8</v>
@@ -1505,19 +1493,19 @@
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>265</v>
+        <v>259</v>
       </c>
       <c r="B3" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="C3" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="D3" t="s">
         <v>11</v>
       </c>
       <c r="E3" t="s">
-        <v>267</v>
+        <v>261</v>
       </c>
       <c r="F3" t="s">
         <v>8</v>
@@ -1528,19 +1516,19 @@
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>265</v>
+        <v>259</v>
       </c>
       <c r="B4" t="s">
-        <v>351</v>
+        <v>343</v>
       </c>
       <c r="C4" t="s">
-        <v>352</v>
+        <v>344</v>
       </c>
       <c r="D4" t="s">
-        <v>353</v>
+        <v>345</v>
       </c>
       <c r="E4" t="s">
-        <v>354</v>
+        <v>346</v>
       </c>
       <c r="F4" t="s">
         <v>8</v>
@@ -1551,19 +1539,19 @@
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>265</v>
+        <v>259</v>
       </c>
       <c r="B5" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="C5" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="D5" t="s">
         <v>12</v>
       </c>
       <c r="E5" t="s">
-        <v>268</v>
+        <v>262</v>
       </c>
       <c r="F5" t="s">
         <v>8</v>
@@ -1574,19 +1562,19 @@
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>265</v>
+        <v>259</v>
       </c>
       <c r="B6" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="C6" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="D6" t="s">
         <v>13</v>
       </c>
       <c r="E6" t="s">
-        <v>269</v>
+        <v>263</v>
       </c>
       <c r="F6" t="s">
         <v>8</v>
@@ -1597,19 +1585,19 @@
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>265</v>
+        <v>259</v>
       </c>
       <c r="B7" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="C7" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="D7" t="s">
         <v>14</v>
       </c>
       <c r="E7" t="s">
-        <v>270</v>
+        <v>264</v>
       </c>
       <c r="F7" t="s">
         <v>8</v>
@@ -1620,19 +1608,19 @@
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>265</v>
+        <v>259</v>
       </c>
       <c r="B8" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="C8" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="D8" t="s">
         <v>15</v>
       </c>
       <c r="E8" t="s">
-        <v>271</v>
+        <v>265</v>
       </c>
       <c r="F8" t="s">
         <v>8</v>
@@ -1643,19 +1631,19 @@
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>265</v>
+        <v>259</v>
       </c>
       <c r="B9" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="C9" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="D9" t="s">
         <v>16</v>
       </c>
       <c r="E9" t="s">
-        <v>272</v>
+        <v>266</v>
       </c>
       <c r="F9" t="s">
         <v>8</v>
@@ -1666,19 +1654,19 @@
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>265</v>
+        <v>259</v>
       </c>
       <c r="B10" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="C10" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="D10" t="s">
         <v>17</v>
       </c>
       <c r="E10" t="s">
-        <v>273</v>
+        <v>267</v>
       </c>
       <c r="F10" t="s">
         <v>8</v>
@@ -1689,19 +1677,19 @@
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>265</v>
+        <v>259</v>
       </c>
       <c r="B11" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="C11" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="D11" t="s">
         <v>18</v>
       </c>
       <c r="E11" t="s">
-        <v>274</v>
+        <v>268</v>
       </c>
       <c r="F11" t="s">
         <v>8</v>
@@ -1712,19 +1700,19 @@
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>265</v>
+        <v>259</v>
       </c>
       <c r="B12" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="C12" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="D12" t="s">
         <v>19</v>
       </c>
       <c r="E12" t="s">
-        <v>275</v>
+        <v>269</v>
       </c>
       <c r="F12" t="s">
         <v>8</v>
@@ -1735,19 +1723,19 @@
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>265</v>
+        <v>259</v>
       </c>
       <c r="B13" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="C13" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="D13" t="s">
         <v>20</v>
       </c>
       <c r="E13" t="s">
-        <v>276</v>
+        <v>270</v>
       </c>
       <c r="F13" t="s">
         <v>8</v>
@@ -1758,19 +1746,19 @@
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>265</v>
+        <v>259</v>
       </c>
       <c r="B14" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="C14" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="D14" t="s">
         <v>21</v>
       </c>
       <c r="E14" t="s">
-        <v>277</v>
+        <v>271</v>
       </c>
       <c r="F14" t="s">
         <v>8</v>
@@ -1781,19 +1769,19 @@
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>265</v>
+        <v>259</v>
       </c>
       <c r="B15" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="C15" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="D15" t="s">
         <v>22</v>
       </c>
       <c r="E15" t="s">
-        <v>278</v>
+        <v>272</v>
       </c>
       <c r="F15" t="s">
         <v>8</v>
@@ -1804,19 +1792,19 @@
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>265</v>
+        <v>259</v>
       </c>
       <c r="B16" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="C16" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="D16" t="s">
         <v>23</v>
       </c>
       <c r="E16" t="s">
-        <v>279</v>
+        <v>273</v>
       </c>
       <c r="F16" t="s">
         <v>8</v>
@@ -1827,19 +1815,19 @@
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>265</v>
+        <v>259</v>
       </c>
       <c r="B17" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="C17" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="D17" t="s">
         <v>24</v>
       </c>
       <c r="E17" t="s">
-        <v>280</v>
+        <v>274</v>
       </c>
       <c r="F17" t="s">
         <v>8</v>
@@ -1850,19 +1838,19 @@
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>265</v>
+        <v>259</v>
       </c>
       <c r="B18" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="C18" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="D18" t="s">
         <v>25</v>
       </c>
       <c r="E18" t="s">
-        <v>281</v>
+        <v>275</v>
       </c>
       <c r="F18" t="s">
         <v>8</v>
@@ -1873,19 +1861,19 @@
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>265</v>
+        <v>259</v>
       </c>
       <c r="B19" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="C19" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="D19" t="s">
         <v>26</v>
       </c>
       <c r="E19" t="s">
-        <v>282</v>
+        <v>276</v>
       </c>
       <c r="F19" t="s">
         <v>8</v>
@@ -1896,19 +1884,19 @@
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>265</v>
+        <v>259</v>
       </c>
       <c r="B20" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="C20" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="D20" t="s">
         <v>27</v>
       </c>
       <c r="E20" t="s">
-        <v>283</v>
+        <v>277</v>
       </c>
       <c r="F20" t="s">
         <v>8</v>
@@ -1919,19 +1907,19 @@
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>265</v>
+        <v>259</v>
       </c>
       <c r="B21" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="C21" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="D21" t="s">
         <v>28</v>
       </c>
       <c r="E21" t="s">
-        <v>284</v>
+        <v>278</v>
       </c>
       <c r="F21" t="s">
         <v>8</v>
@@ -1942,19 +1930,19 @@
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>265</v>
+        <v>259</v>
       </c>
       <c r="B22" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="C22" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="D22" t="s">
         <v>29</v>
       </c>
       <c r="E22" t="s">
-        <v>285</v>
+        <v>279</v>
       </c>
       <c r="F22" t="s">
         <v>8</v>
@@ -1965,19 +1953,19 @@
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>265</v>
+        <v>259</v>
       </c>
       <c r="B23" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="C23" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="D23" t="s">
         <v>30</v>
       </c>
       <c r="E23" t="s">
-        <v>286</v>
+        <v>280</v>
       </c>
       <c r="F23" t="s">
         <v>8</v>
@@ -1988,19 +1976,19 @@
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>265</v>
+        <v>259</v>
       </c>
       <c r="B24" t="s">
-        <v>116</v>
+        <v>355</v>
       </c>
       <c r="C24" t="s">
-        <v>201</v>
+        <v>356</v>
       </c>
       <c r="D24" t="s">
-        <v>31</v>
+        <v>357</v>
       </c>
       <c r="E24" t="s">
-        <v>287</v>
+        <v>358</v>
       </c>
       <c r="F24" t="s">
         <v>8</v>
@@ -2011,19 +1999,19 @@
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>265</v>
+        <v>259</v>
       </c>
       <c r="B25" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="C25" t="s">
-        <v>202</v>
+        <v>197</v>
       </c>
       <c r="D25" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E25" t="s">
-        <v>288</v>
+        <v>281</v>
       </c>
       <c r="F25" t="s">
         <v>8</v>
@@ -2034,19 +2022,19 @@
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>265</v>
+        <v>259</v>
       </c>
       <c r="B26" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="C26" t="s">
-        <v>203</v>
+        <v>198</v>
       </c>
       <c r="D26" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E26" t="s">
-        <v>289</v>
+        <v>282</v>
       </c>
       <c r="F26" t="s">
         <v>8</v>
@@ -2057,19 +2045,19 @@
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>265</v>
+        <v>259</v>
       </c>
       <c r="B27" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="C27" t="s">
-        <v>204</v>
+        <v>199</v>
       </c>
       <c r="D27" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E27" t="s">
-        <v>290</v>
+        <v>283</v>
       </c>
       <c r="F27" t="s">
         <v>8</v>
@@ -2080,19 +2068,19 @@
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>265</v>
+        <v>259</v>
       </c>
       <c r="B28" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="C28" t="s">
-        <v>205</v>
+        <v>200</v>
       </c>
       <c r="D28" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E28" t="s">
-        <v>291</v>
+        <v>284</v>
       </c>
       <c r="F28" t="s">
         <v>8</v>
@@ -2103,19 +2091,19 @@
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>265</v>
+        <v>259</v>
       </c>
       <c r="B29" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="C29" t="s">
-        <v>206</v>
+        <v>201</v>
       </c>
       <c r="D29" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E29" t="s">
-        <v>292</v>
+        <v>285</v>
       </c>
       <c r="F29" t="s">
         <v>8</v>
@@ -2126,19 +2114,19 @@
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>265</v>
+        <v>259</v>
       </c>
       <c r="B30" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="C30" t="s">
-        <v>207</v>
+        <v>202</v>
       </c>
       <c r="D30" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E30" t="s">
-        <v>293</v>
+        <v>286</v>
       </c>
       <c r="F30" t="s">
         <v>8</v>
@@ -2149,19 +2137,19 @@
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>265</v>
+        <v>259</v>
       </c>
       <c r="B31" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="C31" t="s">
-        <v>208</v>
+        <v>203</v>
       </c>
       <c r="D31" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E31" t="s">
-        <v>294</v>
+        <v>287</v>
       </c>
       <c r="F31" t="s">
         <v>8</v>
@@ -2172,19 +2160,19 @@
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>265</v>
+        <v>259</v>
       </c>
       <c r="B32" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="C32" t="s">
-        <v>209</v>
+        <v>204</v>
       </c>
       <c r="D32" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E32" t="s">
-        <v>295</v>
+        <v>288</v>
       </c>
       <c r="F32" t="s">
         <v>8</v>
@@ -2195,19 +2183,19 @@
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>265</v>
+        <v>259</v>
       </c>
       <c r="B33" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="C33" t="s">
-        <v>210</v>
+        <v>205</v>
       </c>
       <c r="D33" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E33" t="s">
-        <v>296</v>
+        <v>289</v>
       </c>
       <c r="F33" t="s">
         <v>8</v>
@@ -2218,19 +2206,19 @@
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>265</v>
+        <v>259</v>
       </c>
       <c r="B34" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="C34" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
       <c r="D34" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E34" t="s">
-        <v>297</v>
+        <v>290</v>
       </c>
       <c r="F34" t="s">
         <v>8</v>
@@ -2241,19 +2229,19 @@
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>265</v>
+        <v>259</v>
       </c>
       <c r="B35" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="C35" t="s">
-        <v>212</v>
+        <v>207</v>
       </c>
       <c r="D35" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E35" t="s">
-        <v>298</v>
+        <v>291</v>
       </c>
       <c r="F35" t="s">
         <v>8</v>
@@ -2264,19 +2252,19 @@
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>265</v>
+        <v>259</v>
       </c>
       <c r="B36" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="C36" t="s">
-        <v>213</v>
+        <v>208</v>
       </c>
       <c r="D36" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E36" t="s">
-        <v>299</v>
+        <v>292</v>
       </c>
       <c r="F36" t="s">
         <v>8</v>
@@ -2287,19 +2275,19 @@
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>265</v>
+        <v>259</v>
       </c>
       <c r="B37" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="C37" t="s">
-        <v>214</v>
+        <v>209</v>
       </c>
       <c r="D37" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E37" t="s">
-        <v>300</v>
+        <v>293</v>
       </c>
       <c r="F37" t="s">
         <v>8</v>
@@ -2310,19 +2298,19 @@
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>265</v>
+        <v>259</v>
       </c>
       <c r="B38" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="C38" t="s">
-        <v>215</v>
+        <v>210</v>
       </c>
       <c r="D38" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E38" t="s">
-        <v>301</v>
+        <v>294</v>
       </c>
       <c r="F38" t="s">
         <v>8</v>
@@ -2333,19 +2321,19 @@
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>265</v>
+        <v>259</v>
       </c>
       <c r="B39" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="C39" t="s">
-        <v>216</v>
+        <v>211</v>
       </c>
       <c r="D39" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E39" t="s">
-        <v>302</v>
+        <v>295</v>
       </c>
       <c r="F39" t="s">
         <v>8</v>
@@ -2356,19 +2344,19 @@
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>265</v>
+        <v>259</v>
       </c>
       <c r="B40" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="C40" t="s">
-        <v>217</v>
+        <v>212</v>
       </c>
       <c r="D40" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E40" t="s">
-        <v>303</v>
+        <v>296</v>
       </c>
       <c r="F40" t="s">
         <v>8</v>
@@ -2379,19 +2367,19 @@
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>265</v>
+        <v>259</v>
       </c>
       <c r="B41" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="C41" t="s">
-        <v>218</v>
+        <v>213</v>
       </c>
       <c r="D41" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E41" t="s">
-        <v>304</v>
+        <v>297</v>
       </c>
       <c r="F41" t="s">
         <v>8</v>
@@ -2402,19 +2390,19 @@
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>265</v>
+        <v>259</v>
       </c>
       <c r="B42" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="C42" t="s">
-        <v>219</v>
+        <v>214</v>
       </c>
       <c r="D42" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E42" t="s">
-        <v>305</v>
+        <v>298</v>
       </c>
       <c r="F42" t="s">
         <v>8</v>
@@ -2425,19 +2413,19 @@
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>265</v>
+        <v>259</v>
       </c>
       <c r="B43" t="s">
-        <v>359</v>
+        <v>351</v>
       </c>
       <c r="C43" t="s">
-        <v>360</v>
+        <v>352</v>
       </c>
       <c r="D43" t="s">
-        <v>361</v>
+        <v>353</v>
       </c>
       <c r="E43" t="s">
-        <v>362</v>
+        <v>354</v>
       </c>
       <c r="F43" t="s">
         <v>8</v>
@@ -2448,19 +2436,19 @@
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>265</v>
+        <v>259</v>
       </c>
       <c r="B44" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="C44" t="s">
-        <v>220</v>
+        <v>215</v>
       </c>
       <c r="D44" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E44" t="s">
-        <v>306</v>
+        <v>299</v>
       </c>
       <c r="F44" t="s">
         <v>8</v>
@@ -2471,19 +2459,19 @@
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>265</v>
+        <v>259</v>
       </c>
       <c r="B45" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="C45" t="s">
-        <v>221</v>
+        <v>216</v>
       </c>
       <c r="D45" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E45" t="s">
-        <v>307</v>
+        <v>300</v>
       </c>
       <c r="F45" t="s">
         <v>8</v>
@@ -2494,19 +2482,19 @@
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>265</v>
+        <v>259</v>
       </c>
       <c r="B46" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="C46" t="s">
-        <v>222</v>
+        <v>217</v>
       </c>
       <c r="D46" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E46" t="s">
-        <v>308</v>
+        <v>301</v>
       </c>
       <c r="F46" t="s">
         <v>8</v>
@@ -2517,19 +2505,19 @@
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>265</v>
+        <v>259</v>
       </c>
       <c r="B47" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="C47" t="s">
-        <v>223</v>
+        <v>218</v>
       </c>
       <c r="D47" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E47" t="s">
-        <v>309</v>
+        <v>302</v>
       </c>
       <c r="F47" t="s">
         <v>8</v>
@@ -2540,19 +2528,19 @@
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>265</v>
+        <v>259</v>
       </c>
       <c r="B48" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="C48" t="s">
-        <v>224</v>
+        <v>219</v>
       </c>
       <c r="D48" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E48" t="s">
-        <v>310</v>
+        <v>303</v>
       </c>
       <c r="F48" t="s">
         <v>8</v>
@@ -2563,19 +2551,19 @@
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>265</v>
+        <v>259</v>
       </c>
       <c r="B49" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="C49" t="s">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="D49" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E49" t="s">
-        <v>311</v>
+        <v>304</v>
       </c>
       <c r="F49" t="s">
         <v>0</v>
@@ -2586,19 +2574,19 @@
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>265</v>
+        <v>259</v>
       </c>
       <c r="B50" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="C50" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="D50" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E50" t="s">
-        <v>312</v>
+        <v>305</v>
       </c>
       <c r="F50" t="s">
         <v>8</v>
@@ -2609,19 +2597,19 @@
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>265</v>
+        <v>259</v>
       </c>
       <c r="B51" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="C51" t="s">
-        <v>227</v>
+        <v>222</v>
       </c>
       <c r="D51" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E51" t="s">
-        <v>313</v>
+        <v>306</v>
       </c>
       <c r="F51" t="s">
         <v>0</v>
@@ -2632,19 +2620,19 @@
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>265</v>
+        <v>259</v>
       </c>
       <c r="B52" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="C52" t="s">
-        <v>228</v>
+        <v>223</v>
       </c>
       <c r="D52" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E52" t="s">
-        <v>314</v>
+        <v>307</v>
       </c>
       <c r="F52" t="s">
         <v>8</v>
@@ -2655,19 +2643,19 @@
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>265</v>
+        <v>259</v>
       </c>
       <c r="B53" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="C53" t="s">
-        <v>229</v>
+        <v>224</v>
       </c>
       <c r="D53" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E53" t="s">
-        <v>315</v>
+        <v>308</v>
       </c>
       <c r="F53" t="s">
         <v>8</v>
@@ -2678,19 +2666,19 @@
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>265</v>
+        <v>259</v>
       </c>
       <c r="B54" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="C54" t="s">
-        <v>230</v>
+        <v>225</v>
       </c>
       <c r="D54" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E54" t="s">
-        <v>316</v>
+        <v>309</v>
       </c>
       <c r="F54" t="s">
         <v>8</v>
@@ -2701,19 +2689,19 @@
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>265</v>
+        <v>259</v>
       </c>
       <c r="B55" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="C55" t="s">
-        <v>231</v>
+        <v>226</v>
       </c>
       <c r="D55" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E55" t="s">
-        <v>317</v>
+        <v>310</v>
       </c>
       <c r="F55" t="s">
         <v>8</v>
@@ -2724,19 +2712,19 @@
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>265</v>
+        <v>259</v>
       </c>
       <c r="B56" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="C56" t="s">
-        <v>232</v>
+        <v>227</v>
       </c>
       <c r="D56" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E56" t="s">
-        <v>318</v>
+        <v>311</v>
       </c>
       <c r="F56" t="s">
         <v>8</v>
@@ -2747,19 +2735,19 @@
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>265</v>
+        <v>259</v>
       </c>
       <c r="B57" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="C57" t="s">
-        <v>233</v>
+        <v>228</v>
       </c>
       <c r="D57" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E57" t="s">
-        <v>319</v>
+        <v>312</v>
       </c>
       <c r="F57" t="s">
         <v>8</v>
@@ -2770,19 +2758,19 @@
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>265</v>
+        <v>259</v>
       </c>
       <c r="B58" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="C58" t="s">
-        <v>234</v>
+        <v>229</v>
       </c>
       <c r="D58" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E58" t="s">
-        <v>320</v>
+        <v>313</v>
       </c>
       <c r="F58" t="s">
         <v>8</v>
@@ -2793,19 +2781,19 @@
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>265</v>
+        <v>259</v>
       </c>
       <c r="B59" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="C59" t="s">
-        <v>235</v>
+        <v>230</v>
       </c>
       <c r="D59" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E59" t="s">
-        <v>321</v>
+        <v>314</v>
       </c>
       <c r="F59" t="s">
         <v>8</v>
@@ -2816,19 +2804,19 @@
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>265</v>
+        <v>259</v>
       </c>
       <c r="B60" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="C60" t="s">
-        <v>236</v>
+        <v>231</v>
       </c>
       <c r="D60" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E60" t="s">
-        <v>322</v>
+        <v>315</v>
       </c>
       <c r="F60" t="s">
         <v>8</v>
@@ -2839,19 +2827,19 @@
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>265</v>
+        <v>259</v>
       </c>
       <c r="B61" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="C61" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="D61" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E61" t="s">
-        <v>323</v>
+        <v>316</v>
       </c>
       <c r="F61" t="s">
         <v>8</v>
@@ -2862,19 +2850,19 @@
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>265</v>
+        <v>259</v>
       </c>
       <c r="B62" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="C62" t="s">
-        <v>238</v>
+        <v>233</v>
       </c>
       <c r="D62" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E62" t="s">
-        <v>324</v>
+        <v>317</v>
       </c>
       <c r="F62" t="s">
         <v>8</v>
@@ -2885,19 +2873,19 @@
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>265</v>
+        <v>259</v>
       </c>
       <c r="B63" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="C63" t="s">
-        <v>239</v>
+        <v>234</v>
       </c>
       <c r="D63" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E63" t="s">
-        <v>325</v>
+        <v>318</v>
       </c>
       <c r="F63" t="s">
         <v>8</v>
@@ -2908,19 +2896,19 @@
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>265</v>
+        <v>259</v>
       </c>
       <c r="B64" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="C64" t="s">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="D64" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E64" t="s">
-        <v>326</v>
+        <v>319</v>
       </c>
       <c r="F64" t="s">
         <v>8</v>
@@ -2931,19 +2919,19 @@
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>265</v>
+        <v>259</v>
       </c>
       <c r="B65" t="s">
-        <v>355</v>
+        <v>347</v>
       </c>
       <c r="C65" t="s">
-        <v>356</v>
+        <v>348</v>
       </c>
       <c r="D65" t="s">
-        <v>357</v>
+        <v>349</v>
       </c>
       <c r="E65" t="s">
-        <v>358</v>
+        <v>350</v>
       </c>
       <c r="F65" t="s">
         <v>8</v>
@@ -2954,19 +2942,19 @@
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>265</v>
+        <v>259</v>
       </c>
       <c r="B66" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="C66" t="s">
-        <v>241</v>
+        <v>236</v>
       </c>
       <c r="D66" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E66" t="s">
-        <v>327</v>
+        <v>320</v>
       </c>
       <c r="F66" t="s">
         <v>8</v>
@@ -2977,19 +2965,19 @@
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>265</v>
+        <v>259</v>
       </c>
       <c r="B67" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="C67" t="s">
-        <v>242</v>
+        <v>237</v>
       </c>
       <c r="D67" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E67" t="s">
-        <v>328</v>
+        <v>321</v>
       </c>
       <c r="F67" t="s">
         <v>8</v>
@@ -3000,19 +2988,19 @@
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>265</v>
+        <v>259</v>
       </c>
       <c r="B68" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="C68" t="s">
-        <v>243</v>
+        <v>238</v>
       </c>
       <c r="D68" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E68" t="s">
-        <v>329</v>
+        <v>322</v>
       </c>
       <c r="F68" t="s">
         <v>8</v>
@@ -3023,19 +3011,19 @@
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>265</v>
+        <v>259</v>
       </c>
       <c r="B69" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="C69" t="s">
-        <v>244</v>
+        <v>239</v>
       </c>
       <c r="D69" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E69" t="s">
-        <v>330</v>
+        <v>323</v>
       </c>
       <c r="F69" t="s">
         <v>8</v>
@@ -3046,19 +3034,19 @@
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>265</v>
+        <v>259</v>
       </c>
       <c r="B70" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="C70" t="s">
-        <v>245</v>
+        <v>240</v>
       </c>
       <c r="D70" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E70" t="s">
-        <v>331</v>
+        <v>324</v>
       </c>
       <c r="F70" t="s">
         <v>8</v>
@@ -3069,19 +3057,19 @@
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>265</v>
+        <v>259</v>
       </c>
       <c r="B71" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="C71" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="D71" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E71" t="s">
-        <v>332</v>
+        <v>325</v>
       </c>
       <c r="F71" t="s">
         <v>8</v>
@@ -3092,19 +3080,19 @@
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>265</v>
+        <v>259</v>
       </c>
       <c r="B72" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="C72" t="s">
-        <v>247</v>
+        <v>242</v>
       </c>
       <c r="D72" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E72" t="s">
-        <v>333</v>
+        <v>326</v>
       </c>
       <c r="F72" t="s">
         <v>8</v>
@@ -3115,19 +3103,19 @@
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>265</v>
+        <v>259</v>
       </c>
       <c r="B73" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="C73" t="s">
-        <v>248</v>
+        <v>243</v>
       </c>
       <c r="D73" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E73" t="s">
-        <v>334</v>
+        <v>327</v>
       </c>
       <c r="F73" t="s">
         <v>8</v>
@@ -3138,19 +3126,19 @@
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>265</v>
+        <v>259</v>
       </c>
       <c r="B74" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="C74" t="s">
-        <v>249</v>
+        <v>244</v>
       </c>
       <c r="D74" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E74" t="s">
-        <v>335</v>
+        <v>328</v>
       </c>
       <c r="F74" t="s">
         <v>8</v>
@@ -3161,19 +3149,19 @@
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>265</v>
+        <v>259</v>
       </c>
       <c r="B75" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="C75" t="s">
-        <v>250</v>
+        <v>245</v>
       </c>
       <c r="D75" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E75" t="s">
-        <v>336</v>
+        <v>329</v>
       </c>
       <c r="F75" t="s">
         <v>8</v>
@@ -3184,19 +3172,19 @@
     </row>
     <row r="76" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>265</v>
+        <v>259</v>
       </c>
       <c r="B76" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="C76" t="s">
-        <v>251</v>
+        <v>246</v>
       </c>
       <c r="D76" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E76" t="s">
-        <v>337</v>
+        <v>330</v>
       </c>
       <c r="F76" t="s">
         <v>8</v>
@@ -3207,19 +3195,19 @@
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>265</v>
+        <v>259</v>
       </c>
       <c r="B77" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="C77" t="s">
-        <v>252</v>
+        <v>247</v>
       </c>
       <c r="D77" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E77" t="s">
-        <v>338</v>
+        <v>331</v>
       </c>
       <c r="F77" t="s">
         <v>8</v>
@@ -3230,19 +3218,19 @@
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>265</v>
+        <v>259</v>
       </c>
       <c r="B78" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="C78" t="s">
-        <v>253</v>
+        <v>248</v>
       </c>
       <c r="D78" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E78" t="s">
-        <v>339</v>
+        <v>332</v>
       </c>
       <c r="F78" t="s">
         <v>8</v>
@@ -3253,19 +3241,19 @@
     </row>
     <row r="79" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>265</v>
+        <v>259</v>
       </c>
       <c r="B79" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="C79" t="s">
-        <v>254</v>
+        <v>249</v>
       </c>
       <c r="D79" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E79" t="s">
-        <v>340</v>
+        <v>333</v>
       </c>
       <c r="F79" t="s">
         <v>8</v>
@@ -3276,19 +3264,19 @@
     </row>
     <row r="80" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>265</v>
+        <v>259</v>
       </c>
       <c r="B80" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="C80" t="s">
-        <v>255</v>
+        <v>250</v>
       </c>
       <c r="D80" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E80" t="s">
-        <v>341</v>
+        <v>334</v>
       </c>
       <c r="F80" t="s">
         <v>8</v>
@@ -3299,19 +3287,19 @@
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>265</v>
+        <v>259</v>
       </c>
       <c r="B81" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="C81" t="s">
-        <v>256</v>
+        <v>251</v>
       </c>
       <c r="D81" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E81" t="s">
-        <v>342</v>
+        <v>335</v>
       </c>
       <c r="F81" t="s">
         <v>8</v>
@@ -3322,19 +3310,19 @@
     </row>
     <row r="82" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>265</v>
+        <v>259</v>
       </c>
       <c r="B82" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="C82" t="s">
-        <v>257</v>
+        <v>252</v>
       </c>
       <c r="D82" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E82" t="s">
-        <v>343</v>
+        <v>336</v>
       </c>
       <c r="F82" t="s">
         <v>8</v>
@@ -3345,19 +3333,19 @@
     </row>
     <row r="83" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>265</v>
+        <v>259</v>
       </c>
       <c r="B83" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="C83" t="s">
-        <v>258</v>
+        <v>253</v>
       </c>
       <c r="D83" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E83" t="s">
-        <v>344</v>
+        <v>337</v>
       </c>
       <c r="F83" t="s">
         <v>8</v>
@@ -3368,19 +3356,19 @@
     </row>
     <row r="84" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>265</v>
+        <v>259</v>
       </c>
       <c r="B84" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="C84" t="s">
-        <v>259</v>
+        <v>254</v>
       </c>
       <c r="D84" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E84" t="s">
-        <v>345</v>
+        <v>338</v>
       </c>
       <c r="F84" t="s">
         <v>8</v>
@@ -3391,19 +3379,19 @@
     </row>
     <row r="85" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>265</v>
+        <v>259</v>
       </c>
       <c r="B85" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="C85" t="s">
-        <v>260</v>
+        <v>255</v>
       </c>
       <c r="D85" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E85" t="s">
-        <v>346</v>
+        <v>339</v>
       </c>
       <c r="F85" t="s">
         <v>8</v>
@@ -3414,19 +3402,19 @@
     </row>
     <row r="86" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>265</v>
+        <v>259</v>
       </c>
       <c r="B86" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="C86" t="s">
-        <v>261</v>
+        <v>256</v>
       </c>
       <c r="D86" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E86" t="s">
-        <v>347</v>
+        <v>340</v>
       </c>
       <c r="F86" t="s">
         <v>8</v>
@@ -3437,19 +3425,19 @@
     </row>
     <row r="87" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>265</v>
+        <v>259</v>
       </c>
       <c r="B87" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="C87" t="s">
-        <v>262</v>
+        <v>257</v>
       </c>
       <c r="D87" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="E87" t="s">
-        <v>348</v>
+        <v>341</v>
       </c>
       <c r="F87" t="s">
         <v>8</v>
@@ -3460,47 +3448,24 @@
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>265</v>
+        <v>259</v>
       </c>
       <c r="B88" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="C88" t="s">
-        <v>263</v>
+        <v>258</v>
       </c>
       <c r="D88" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E88" t="s">
-        <v>349</v>
+        <v>342</v>
       </c>
       <c r="F88" t="s">
         <v>8</v>
       </c>
       <c r="G88" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="89" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A89" t="s">
-        <v>265</v>
-      </c>
-      <c r="B89" t="s">
-        <v>179</v>
-      </c>
-      <c r="C89" t="s">
-        <v>264</v>
-      </c>
-      <c r="D89" t="s">
-        <v>94</v>
-      </c>
-      <c r="E89" t="s">
-        <v>350</v>
-      </c>
-      <c r="F89" t="s">
-        <v>8</v>
-      </c>
-      <c r="G89" t="s">
         <v>9</v>
       </c>
     </row>
